--- a/artfynd/A 715-2023 artfynd.xlsx
+++ b/artfynd/A 715-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 715-2023 artfynd.xlsx
+++ b/artfynd/A 715-2023 artfynd.xlsx
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 715-2023 artfynd.xlsx
+++ b/artfynd/A 715-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105947794</v>
+        <v>105949597</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjäreberget, Ång</t>
+          <t>Tjärnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609489.0179723159</v>
+        <v>609627</v>
       </c>
       <c r="R2" t="n">
-        <v>7023224.527826144</v>
+        <v>7023106</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,51 +773,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105947762</v>
+        <v>105950317</v>
       </c>
       <c r="B3" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjäreberget, Ång</t>
+          <t>Tjärnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609444.711546827</v>
+        <v>609751</v>
       </c>
       <c r="R3" t="n">
-        <v>7023242.805161252</v>
+        <v>7023117</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,26 +842,16 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -889,12 +859,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rasmus Lenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Rasmus Lenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -904,12 +874,7 @@
         <v>107297588</v>
       </c>
       <c r="B4" t="n">
-        <v>89967</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609444.711546827</v>
+        <v>609445</v>
       </c>
       <c r="R4" t="n">
-        <v>7023242.805161252</v>
+        <v>7023242</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,19 +942,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,15 +972,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105950328</v>
+        <v>105949553</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>609858.0417494342</v>
+        <v>609643</v>
       </c>
       <c r="R5" t="n">
-        <v>7023139.990946184</v>
+        <v>7023111</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,19 +1041,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,15 +1070,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105949553</v>
+        <v>105950238</v>
       </c>
       <c r="B6" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>609642.3931722931</v>
+        <v>609748</v>
       </c>
       <c r="R6" t="n">
-        <v>7023111.480498624</v>
+        <v>7023129</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1204,19 +1139,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,37 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105950324</v>
+        <v>105950328</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>609861.1290859708</v>
+        <v>609858</v>
       </c>
       <c r="R7" t="n">
-        <v>7023141.895589369</v>
+        <v>7023140</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,19 +1237,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105950317</v>
+        <v>105950494</v>
       </c>
       <c r="B8" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,21 +1277,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609750.3077707707</v>
+        <v>609704</v>
       </c>
       <c r="R8" t="n">
-        <v>7023116.517129303</v>
+        <v>7023159</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1337,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1347,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,27 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Lenander</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Lenander</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105950238</v>
+        <v>105950324</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609747.1941189246</v>
+        <v>609861</v>
       </c>
       <c r="R9" t="n">
-        <v>7023128.553923509</v>
+        <v>7023142</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,19 +1443,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,12 +1475,7 @@
         <v>105949925</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1623,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609661.2144056129</v>
+        <v>609661</v>
       </c>
       <c r="R10" t="n">
-        <v>7023127.414812577</v>
+        <v>7023127</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,19 +1541,9 @@
           <t>2023-01-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,119 +1567,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>105950494</v>
-      </c>
-      <c r="B11" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tjärnbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>609703.81979387</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7023159.003424637</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Resele</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-01-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 715-2023 artfynd.xlsx
+++ b/artfynd/A 715-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105949597</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105950317</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -969,6 +984,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107297588</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1067,6 +1087,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105949553</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105950238</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105950328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105950494</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105950324</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1567,8 +1612,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105949925</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>